--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_individual_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_individual_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.04969362208244506</v>
       </c>
       <c r="C2" t="n">
-        <v>62127720</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>62127720</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>42102338</v>
+        <v>3686928</v>
       </c>
       <c r="L2" t="n">
-        <v>23441316</v>
+        <v>1779276</v>
       </c>
       <c r="M2" t="n">
-        <v>5873600</v>
+        <v>385252</v>
       </c>
       <c r="N2" t="n">
-        <v>320818</v>
+        <v>14971</v>
       </c>
       <c r="O2" t="n">
-        <v>3543324</v>
+        <v>245114</v>
       </c>
       <c r="P2" t="n">
-        <v>1466926</v>
+        <v>108372</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998925924301147</v>
+        <v>0.9997877478599548</v>
       </c>
       <c r="R2" t="n">
-        <v>0.855153501033783</v>
+        <v>0.7487995624542236</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7265979051589966</v>
+        <v>0.551543653011322</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6289702653884888</v>
+        <v>0.4126697778701782</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4469300508499146</v>
+        <v>0.2093670517206192</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6969688534736633</v>
+        <v>0.4823388755321503</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7584799528121948</v>
+        <v>0.5606791973114014</v>
       </c>
       <c r="X2" t="n">
-        <v>62127720</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>62127720</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>40931866</v>
+        <v>3625657</v>
       </c>
       <c r="AG2" t="n">
-        <v>21825235</v>
+        <v>1702389</v>
       </c>
       <c r="AH2" t="n">
-        <v>5311771</v>
+        <v>359888</v>
       </c>
       <c r="AI2" t="n">
-        <v>286298</v>
+        <v>13986</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3264326</v>
+        <v>229809</v>
       </c>
       <c r="AK2" t="n">
-        <v>1375892</v>
+        <v>101680</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8289598822593689</v>
+        <v>0.7342748641967773</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6811686158180237</v>
+        <v>0.5313179492950439</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.573558509349823</v>
+        <v>0.388602614402771</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3239471316337585</v>
+        <v>0.1582520604133606</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6425155401229858</v>
+        <v>0.4523318409919739</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7119272947311401</v>
+        <v>0.5261224508285522</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.01495173573263417</v>
       </c>
       <c r="C3" t="n">
-        <v>2368</v>
+        <v>553</v>
       </c>
       <c r="D3" t="n">
-        <v>42102338</v>
+        <v>3686928</v>
       </c>
       <c r="E3" t="n">
-        <v>6256152</v>
+        <v>1035700</v>
       </c>
       <c r="F3" t="n">
-        <v>412864</v>
+        <v>87790</v>
       </c>
       <c r="G3" t="n">
-        <v>56850</v>
+        <v>9335</v>
       </c>
       <c r="H3" t="n">
-        <v>26697</v>
+        <v>8832</v>
       </c>
       <c r="I3" t="n">
-        <v>4418</v>
+        <v>1524</v>
       </c>
       <c r="J3" t="n">
-        <v>98569608</v>
+        <v>9856309</v>
       </c>
       <c r="K3" t="n">
-        <v>104710991</v>
+        <v>10002881</v>
       </c>
       <c r="L3" t="n">
-        <v>119417885</v>
+        <v>11331255</v>
       </c>
       <c r="M3" t="n">
-        <v>147911545</v>
+        <v>14582400</v>
       </c>
       <c r="N3" t="n">
-        <v>159418319</v>
+        <v>15924471</v>
       </c>
       <c r="O3" t="n">
-        <v>154065415</v>
+        <v>15295689</v>
       </c>
       <c r="P3" t="n">
-        <v>158302279</v>
+        <v>15791680</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8616636395454407</v>
+        <v>0.7632344961166382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7220335602760315</v>
+        <v>0.540414571762085</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6296999454498291</v>
+        <v>0.4099768996238708</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3610079288482666</v>
+        <v>0.1674720942974091</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6950415968894958</v>
+        <v>0.4790685772895813</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7582529187202454</v>
+        <v>0.5591806173324585</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>40931866</v>
+        <v>3625657</v>
       </c>
       <c r="Z3" t="n">
-        <v>7260474</v>
+        <v>1076099</v>
       </c>
       <c r="AA3" t="n">
-        <v>475615</v>
+        <v>95172</v>
       </c>
       <c r="AB3" t="n">
-        <v>149460</v>
+        <v>19777</v>
       </c>
       <c r="AC3" t="n">
-        <v>38103</v>
+        <v>11762</v>
       </c>
       <c r="AD3" t="n">
-        <v>6169</v>
+        <v>2195</v>
       </c>
       <c r="AE3" t="n">
-        <v>98576280</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>103396799</v>
+        <v>9927657</v>
       </c>
       <c r="AG3" t="n">
-        <v>118022678</v>
+        <v>11276274</v>
       </c>
       <c r="AH3" t="n">
-        <v>147427074</v>
+        <v>14564488</v>
       </c>
       <c r="AI3" t="n">
-        <v>159217845</v>
+        <v>15906614</v>
       </c>
       <c r="AJ3" t="n">
-        <v>153789783</v>
+        <v>15280508</v>
       </c>
       <c r="AK3" t="n">
-        <v>158212649</v>
+        <v>15785012</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8377088308334351</v>
+        <v>0.7505507469177246</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6722554564476013</v>
+        <v>0.5170618891716003</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5694671273231506</v>
+        <v>0.3829850554466248</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3221634924411774</v>
+        <v>0.1564534604549408</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6403146386146545</v>
+        <v>0.4491553604602814</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.711197555065155</v>
+        <v>0.524651050567627</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.09930228843434777</v>
       </c>
       <c r="C4" t="n">
-        <v>1022</v>
+        <v>221</v>
       </c>
       <c r="D4" t="n">
-        <v>6640140</v>
+        <v>1123210</v>
       </c>
       <c r="E4" t="n">
-        <v>23441316</v>
+        <v>1779276</v>
       </c>
       <c r="F4" t="n">
-        <v>1985439</v>
+        <v>300327</v>
       </c>
       <c r="G4" t="n">
-        <v>85713</v>
+        <v>15255</v>
       </c>
       <c r="H4" t="n">
-        <v>273102</v>
+        <v>63362</v>
       </c>
       <c r="I4" t="n">
-        <v>38955</v>
+        <v>10777</v>
       </c>
       <c r="J4" t="n">
-        <v>6672</v>
+        <v>1319</v>
       </c>
       <c r="K4" t="n">
-        <v>7131322</v>
+        <v>1236857</v>
       </c>
       <c r="L4" t="n">
-        <v>8820428</v>
+        <v>1446717</v>
       </c>
       <c r="M4" t="n">
-        <v>3464838</v>
+        <v>548308</v>
       </c>
       <c r="N4" t="n">
-        <v>397008</v>
+        <v>56535</v>
       </c>
       <c r="O4" t="n">
-        <v>1540582</v>
+        <v>263064</v>
       </c>
       <c r="P4" t="n">
-        <v>467108</v>
+        <v>84915</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999462962150574</v>
+        <v>0.999893844127655</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8583962321281433</v>
+        <v>0.7559481263160706</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7243084907531738</v>
+        <v>0.5459223985671997</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6293349266052246</v>
+        <v>0.4113189280033112</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3994001746177673</v>
+        <v>0.1860907375812531</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6960039138793945</v>
+        <v>0.4806981682777405</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7583663463592529</v>
+        <v>0.5599288940429688</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>7818406</v>
+        <v>1177970</v>
       </c>
       <c r="Z4" t="n">
-        <v>21825235</v>
+        <v>1702389</v>
       </c>
       <c r="AA4" t="n">
-        <v>2273688</v>
+        <v>306468</v>
       </c>
       <c r="AB4" t="n">
-        <v>152950</v>
+        <v>21732</v>
       </c>
       <c r="AC4" t="n">
-        <v>343900</v>
+        <v>71063</v>
       </c>
       <c r="AD4" t="n">
-        <v>51508</v>
+        <v>12806</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>8445514</v>
+        <v>1312081</v>
       </c>
       <c r="AG4" t="n">
-        <v>10215635</v>
+        <v>1501698</v>
       </c>
       <c r="AH4" t="n">
-        <v>3949309</v>
+        <v>566220</v>
       </c>
       <c r="AI4" t="n">
-        <v>597482</v>
+        <v>74392</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1816214</v>
+        <v>278245</v>
       </c>
       <c r="AK4" t="n">
-        <v>556738</v>
+        <v>91583</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8333114385604858</v>
+        <v>0.742323637008667</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.676682710647583</v>
+        <v>0.524092972278595</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5715054869651794</v>
+        <v>0.3857733905315399</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.323052853345871</v>
+        <v>0.1573476195335388</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6414132118225098</v>
+        <v>0.4507379829883575</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7115622758865356</v>
+        <v>0.5253856778144836</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1107</v>
+        <v>218</v>
       </c>
       <c r="D5" t="n">
-        <v>344390</v>
+        <v>84285</v>
       </c>
       <c r="E5" t="n">
-        <v>2088893</v>
+        <v>309400</v>
       </c>
       <c r="F5" t="n">
-        <v>5873600</v>
+        <v>385252</v>
       </c>
       <c r="G5" t="n">
-        <v>139636</v>
+        <v>17592</v>
       </c>
       <c r="H5" t="n">
-        <v>777692</v>
+        <v>120518</v>
       </c>
       <c r="I5" t="n">
-        <v>102299</v>
+        <v>22427</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6759349</v>
+        <v>1143734</v>
       </c>
       <c r="L5" t="n">
-        <v>9024371</v>
+        <v>1513152</v>
       </c>
       <c r="M5" t="n">
-        <v>3454017</v>
+        <v>554440</v>
       </c>
       <c r="N5" t="n">
-        <v>567855</v>
+        <v>74423</v>
       </c>
       <c r="O5" t="n">
-        <v>1554679</v>
+        <v>266533</v>
       </c>
       <c r="P5" t="n">
-        <v>467687</v>
+        <v>85433</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999584555625916</v>
+        <v>0.9999179244041443</v>
       </c>
       <c r="R5" t="n">
-        <v>0.91356360912323</v>
+        <v>0.8518648743629456</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8889585733413696</v>
+        <v>0.8158186078071594</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9569466114044189</v>
+        <v>0.9313801527023315</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9939960241317749</v>
+        <v>0.9918509721755981</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9807393550872803</v>
+        <v>0.9670451879501343</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9941831231117249</v>
+        <v>0.9893999099731445</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>444611</v>
+        <v>99186</v>
       </c>
       <c r="Z5" t="n">
-        <v>2378212</v>
+        <v>313472</v>
       </c>
       <c r="AA5" t="n">
-        <v>5311771</v>
+        <v>359888</v>
       </c>
       <c r="AB5" t="n">
-        <v>165510</v>
+        <v>18421</v>
       </c>
       <c r="AC5" t="n">
-        <v>900772</v>
+        <v>123791</v>
       </c>
       <c r="AD5" t="n">
-        <v>126741</v>
+        <v>24934</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>7929821</v>
+        <v>1205005</v>
       </c>
       <c r="AG5" t="n">
-        <v>10640452</v>
+        <v>1590039</v>
       </c>
       <c r="AH5" t="n">
-        <v>4015846</v>
+        <v>579804</v>
       </c>
       <c r="AI5" t="n">
-        <v>602375</v>
+        <v>75408</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1833677</v>
+        <v>281838</v>
       </c>
       <c r="AK5" t="n">
-        <v>558721</v>
+        <v>92125</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8981025218963623</v>
+        <v>0.8433712720870972</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8702204823493958</v>
+        <v>0.8076129555702209</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9504358768463135</v>
+        <v>0.9286872744560242</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9925337433815002</v>
+        <v>0.9906784892082214</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9772881269454956</v>
+        <v>0.9651481509208679</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9930589199066162</v>
+        <v>0.9885685443878174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1489</v>
+        <v>236</v>
       </c>
       <c r="D6" t="n">
-        <v>116744</v>
+        <v>17458</v>
       </c>
       <c r="E6" t="n">
-        <v>147751</v>
+        <v>22520</v>
       </c>
       <c r="F6" t="n">
-        <v>183011</v>
+        <v>18437</v>
       </c>
       <c r="G6" t="n">
-        <v>320818</v>
+        <v>14971</v>
       </c>
       <c r="H6" t="n">
-        <v>101090</v>
+        <v>12757</v>
       </c>
       <c r="I6" t="n">
-        <v>17770</v>
+        <v>3015</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>135685</v>
+        <v>18527</v>
       </c>
       <c r="Z6" t="n">
-        <v>161747</v>
+        <v>22938</v>
       </c>
       <c r="AA6" t="n">
-        <v>171099</v>
+        <v>17926</v>
       </c>
       <c r="AB6" t="n">
-        <v>286298</v>
+        <v>13986</v>
       </c>
       <c r="AC6" t="n">
-        <v>113385</v>
+        <v>12833</v>
       </c>
       <c r="AD6" t="n">
-        <v>20459</v>
+        <v>3184</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>462</v>
+        <v>66</v>
       </c>
       <c r="D7" t="n">
-        <v>28768</v>
+        <v>11219</v>
       </c>
       <c r="E7" t="n">
-        <v>299125</v>
+        <v>70612</v>
       </c>
       <c r="F7" t="n">
-        <v>821307</v>
+        <v>125907</v>
       </c>
       <c r="G7" t="n">
-        <v>101351</v>
+        <v>11557</v>
       </c>
       <c r="H7" t="n">
-        <v>3543324</v>
+        <v>245114</v>
       </c>
       <c r="I7" t="n">
-        <v>303666</v>
+        <v>47172</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>44155</v>
+        <v>15141</v>
       </c>
       <c r="Z7" t="n">
-        <v>376853</v>
+        <v>79076</v>
       </c>
       <c r="AA7" t="n">
-        <v>947884</v>
+        <v>127747</v>
       </c>
       <c r="AB7" t="n">
-        <v>112924</v>
+        <v>11410</v>
       </c>
       <c r="AC7" t="n">
-        <v>3264326</v>
+        <v>229809</v>
       </c>
       <c r="AD7" t="n">
-        <v>351861</v>
+        <v>48464</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>1280</v>
+        <v>685</v>
       </c>
       <c r="E8" t="n">
-        <v>28507</v>
+        <v>8485</v>
       </c>
       <c r="F8" t="n">
-        <v>62217</v>
+        <v>15847</v>
       </c>
       <c r="G8" t="n">
-        <v>13458</v>
+        <v>2796</v>
       </c>
       <c r="H8" t="n">
-        <v>362001</v>
+        <v>57595</v>
       </c>
       <c r="I8" t="n">
-        <v>1466926</v>
+        <v>108372</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2657</v>
+        <v>1257</v>
       </c>
       <c r="Z8" t="n">
-        <v>38349</v>
+        <v>10113</v>
       </c>
       <c r="AA8" t="n">
-        <v>81023</v>
+        <v>18907</v>
       </c>
       <c r="AB8" t="n">
-        <v>16638</v>
+        <v>3052</v>
       </c>
       <c r="AC8" t="n">
-        <v>420054</v>
+        <v>58796</v>
       </c>
       <c r="AD8" t="n">
-        <v>1375892</v>
+        <v>101680</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
